--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/VIRGINIA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/VIRGINIA_2011.xlsx
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C130">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C453">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C509">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C522">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C527">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C848">
